--- a/artfynd/A 20097-2025 artfynd.xlsx
+++ b/artfynd/A 20097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076358</v>
       </c>
       <c r="B2" t="n">
-        <v>75007</v>
+        <v>75066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127076316</v>
       </c>
       <c r="B3" t="n">
-        <v>79139</v>
+        <v>79170</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127076067</v>
       </c>
       <c r="B4" t="n">
-        <v>79061</v>
+        <v>79092</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>127076431</v>
       </c>
       <c r="B5" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127076438</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127076372</v>
       </c>
       <c r="B7" t="n">
-        <v>82792</v>
+        <v>82852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>127076259</v>
       </c>
       <c r="B8" t="n">
-        <v>91241</v>
+        <v>91315</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20097-2025 artfynd.xlsx
+++ b/artfynd/A 20097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076358</v>
       </c>
       <c r="B2" t="n">
-        <v>75066</v>
+        <v>75069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127076316</v>
       </c>
       <c r="B3" t="n">
-        <v>79170</v>
+        <v>79173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127076067</v>
       </c>
       <c r="B4" t="n">
-        <v>79092</v>
+        <v>79095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>127076431</v>
       </c>
       <c r="B5" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127076438</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127076372</v>
       </c>
       <c r="B7" t="n">
-        <v>82852</v>
+        <v>82855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>127076259</v>
       </c>
       <c r="B8" t="n">
-        <v>91315</v>
+        <v>91321</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20097-2025 artfynd.xlsx
+++ b/artfynd/A 20097-2025 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>127076259</v>
       </c>
       <c r="B8" t="n">
-        <v>91321</v>
+        <v>91322</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20097-2025 artfynd.xlsx
+++ b/artfynd/A 20097-2025 artfynd.xlsx
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127076372</v>
+        <v>127076259</v>
       </c>
       <c r="B7" t="n">
-        <v>82855</v>
+        <v>91322</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451924</v>
+        <v>452075</v>
       </c>
       <c r="R7" t="n">
-        <v>7173368</v>
+        <v>7173602</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127076259</v>
+        <v>127076372</v>
       </c>
       <c r="B8" t="n">
-        <v>91322</v>
+        <v>82855</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1316,21 +1316,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452075</v>
+        <v>451924</v>
       </c>
       <c r="R8" t="n">
-        <v>7173602</v>
+        <v>7173368</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 20097-2025 artfynd.xlsx
+++ b/artfynd/A 20097-2025 artfynd.xlsx
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127076259</v>
+        <v>127076372</v>
       </c>
       <c r="B7" t="n">
-        <v>91322</v>
+        <v>82855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452075</v>
+        <v>451924</v>
       </c>
       <c r="R7" t="n">
-        <v>7173602</v>
+        <v>7173368</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127076372</v>
+        <v>127076259</v>
       </c>
       <c r="B8" t="n">
-        <v>82855</v>
+        <v>91322</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1316,21 +1316,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451924</v>
+        <v>452075</v>
       </c>
       <c r="R8" t="n">
-        <v>7173368</v>
+        <v>7173602</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 20097-2025 artfynd.xlsx
+++ b/artfynd/A 20097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076358</v>
       </c>
       <c r="B2" t="n">
-        <v>75069</v>
+        <v>75073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127076316</v>
       </c>
       <c r="B3" t="n">
-        <v>79173</v>
+        <v>79177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127076067</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79099</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>127076431</v>
       </c>
       <c r="B5" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127076438</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127076259</v>
+        <v>127076372</v>
       </c>
       <c r="B7" t="n">
-        <v>91322</v>
+        <v>82859</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452075</v>
+        <v>451924</v>
       </c>
       <c r="R7" t="n">
-        <v>7173602</v>
+        <v>7173368</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127076372</v>
+        <v>127076259</v>
       </c>
       <c r="B8" t="n">
-        <v>82855</v>
+        <v>91326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1316,21 +1316,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451924</v>
+        <v>452075</v>
       </c>
       <c r="R8" t="n">
-        <v>7173368</v>
+        <v>7173602</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 20097-2025 artfynd.xlsx
+++ b/artfynd/A 20097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076358</v>
       </c>
       <c r="B2" t="n">
-        <v>75073</v>
+        <v>75075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127076316</v>
       </c>
       <c r="B3" t="n">
-        <v>79177</v>
+        <v>79179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127076067</v>
       </c>
       <c r="B4" t="n">
-        <v>79099</v>
+        <v>79101</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>127076431</v>
       </c>
       <c r="B5" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127076438</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127076372</v>
       </c>
       <c r="B7" t="n">
-        <v>82859</v>
+        <v>82861</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>127076259</v>
       </c>
       <c r="B8" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20097-2025 artfynd.xlsx
+++ b/artfynd/A 20097-2025 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>127076259</v>
       </c>
       <c r="B8" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20097-2025 artfynd.xlsx
+++ b/artfynd/A 20097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127076358</v>
       </c>
       <c r="B2" t="n">
-        <v>75075</v>
+        <v>75078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>127076316</v>
       </c>
       <c r="B3" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>127076067</v>
       </c>
       <c r="B4" t="n">
-        <v>79101</v>
+        <v>79104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>127076431</v>
       </c>
       <c r="B5" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127076438</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127076372</v>
       </c>
       <c r="B7" t="n">
-        <v>82861</v>
+        <v>82864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>127076259</v>
       </c>
       <c r="B8" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
